--- a/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,44; 43,34</t>
+          <t>26,04; 43,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,0; 46,9</t>
+          <t>31,97; 46,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 38,63</t>
+          <t>24,38; 38,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,09; 95,87</t>
+          <t>84,44; 96,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,15; 45,11</t>
+          <t>28,68; 44,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,15; 50,54</t>
+          <t>34,74; 50,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,48; 45,61</t>
+          <t>29,29; 44,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,98; 99,36</t>
+          <t>93,74; 99,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,48; 41,59</t>
+          <t>30,05; 41,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,08; 46,12</t>
+          <t>35,1; 46,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 39,53</t>
+          <t>28,91; 39,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,38; 97,26</t>
+          <t>91,24; 97,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 41,71</t>
+          <t>29,76; 41,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,23; 53,06</t>
+          <t>39,36; 52,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,53; 45,38</t>
+          <t>33,0; 45,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,48; 97,88</t>
+          <t>92,98; 97,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,75; 43,08</t>
+          <t>31,92; 42,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,48; 49,97</t>
+          <t>38,14; 50,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,52; 40,67</t>
+          <t>30,03; 40,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,61; 96,04</t>
+          <t>89,32; 95,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,63; 40,56</t>
+          <t>32,02; 40,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41,21; 49,61</t>
+          <t>40,62; 49,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 41,12</t>
+          <t>32,93; 40,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,97; 96,11</t>
+          <t>91,82; 96,05</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,41; 57,12</t>
+          <t>39,5; 56,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,72; 59,19</t>
+          <t>43,26; 60,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,41; 50,93</t>
+          <t>37,33; 50,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,68; 96,87</t>
+          <t>90,72; 96,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,49; 56,72</t>
+          <t>41,14; 57,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,74; 57,09</t>
+          <t>41,34; 56,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,5; 52,52</t>
+          <t>38,02; 52,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,2; 97,31</t>
+          <t>91,02; 97,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,44; 55,13</t>
+          <t>42,7; 54,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,97; 56,05</t>
+          <t>44,62; 56,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,91; 49,21</t>
+          <t>39,97; 50,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,17; 96,74</t>
+          <t>92,54; 96,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,58; 49,89</t>
+          <t>36,36; 49,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,02; 57,02</t>
+          <t>42,44; 57,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,63; 62,19</t>
+          <t>46,34; 61,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,31; 97,73</t>
+          <t>93,32; 97,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,19; 55,27</t>
+          <t>42,88; 55,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,11; 64,74</t>
+          <t>50,56; 65,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,35; 56,16</t>
+          <t>41,01; 56,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,75; 96,96</t>
+          <t>92,18; 97,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,09; 50,34</t>
+          <t>41,43; 50,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,48; 58,59</t>
+          <t>48,85; 59,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,44; 56,18</t>
+          <t>46,25; 56,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,52; 96,81</t>
+          <t>93,5; 96,93</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,09; 43,32</t>
+          <t>36,33; 43,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,08; 50,23</t>
+          <t>43,1; 50,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,94; 45,67</t>
+          <t>39,05; 46,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,52; 96,48</t>
+          <t>93,65; 96,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,43; 46,47</t>
+          <t>39,46; 46,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,3; 51,32</t>
+          <t>44,4; 51,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,88; 44,67</t>
+          <t>37,91; 44,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,08; 96,1</t>
+          <t>92,96; 96,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,83; 43,63</t>
+          <t>38,91; 43,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,8; 49,78</t>
+          <t>44,72; 50,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,31; 44,27</t>
+          <t>39,18; 44,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,84; 95,9</t>
+          <t>93,79; 95,86</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>27312</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32149</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>52736</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32410</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47533</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36779</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>60123</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>59723</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88372</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68928</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>112858</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20460; 34106</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33287; 48661</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25034; 39343</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48560; 55320</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25370; 39072</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>38926; 56765</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28787; 43608</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>57596; 61056</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>50196; 69090</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>75867; 100224</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>58103; 79580</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>108535; 115927</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>66552</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74003</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60715</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>152658</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70104</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85128</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74341</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>170180</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>136656</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>159130</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>135056</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>322838</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>55716; 77526</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>62712; 83215</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>51564; 70441</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>148121; 155965</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>60248; 80388</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>73687; 97323</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>63239; 85703</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>163054; 174825</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>120397; 151311</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>143229; 175983</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>120819; 150358</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>313904; 328347</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>41679</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50258</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63671</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163938</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50803</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50356</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60206</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>201945</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>92482</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100615</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123877</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>365883</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>34155; 49076</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42390; 59095</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53875; 73174</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157745; 168305</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>42486; 59457</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>42092; 57660</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>50254; 69798</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>193402; 207189</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>81014; 103937</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>89148; 112632</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>110502; 138360</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>357546; 373301</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>64602</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57295</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66139</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>264336</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72916</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76055</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63292</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>289921</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>137518</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>133350</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>129431</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>554255</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>54927; 75373</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49025; 66616</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>56587; 75464</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>257058; 269280</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>63510; 82819</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>66590; 85822</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>53317; 73825</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>281585; 296381</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>123946; 151196</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>120768; 146438</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>116601; 143243</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>543189; 563111</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>200145</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222394</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>222674</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>633667</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>722169</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>426378</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>481467</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>457292</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1355836</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>182877; 216941</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>205564; 239769</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>205187; 245939</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>623857; 643158</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>208567; 243856</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>239227; 276099</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>216460; 254440</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>708305; 732249</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>401501; 451997</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>454290; 509320</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>429534; 483422</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1339500; 1368932</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,04; 43,41</t>
+          <t>26,39; 43,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,97; 46,73</t>
+          <t>31,09; 46,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 38,31</t>
+          <t>23,94; 38,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,44; 96,19</t>
+          <t>84,26; 95,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,68; 44,17</t>
+          <t>28,89; 44,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,74; 50,66</t>
+          <t>34,1; 50,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,29; 44,38</t>
+          <t>29,84; 45,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,74; 99,37</t>
+          <t>93,59; 99,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,05; 41,37</t>
+          <t>29,61; 41,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,1; 46,36</t>
+          <t>35,29; 46,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,91; 39,6</t>
+          <t>29,05; 39,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,24; 97,45</t>
+          <t>91,34; 97,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,76; 41,4</t>
+          <t>30,19; 41,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,36; 52,22</t>
+          <t>40,17; 52,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,0; 45,08</t>
+          <t>32,71; 44,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,98; 97,91</t>
+          <t>92,18; 97,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,92; 42,59</t>
+          <t>31,53; 43,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,14; 50,37</t>
+          <t>37,8; 50,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 40,7</t>
+          <t>30,17; 41,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,32; 95,77</t>
+          <t>89,38; 95,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,02; 40,24</t>
+          <t>32,15; 40,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40,62; 49,91</t>
+          <t>40,65; 49,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,93; 40,99</t>
+          <t>33,01; 40,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,82; 96,05</t>
+          <t>91,83; 96,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,5; 56,75</t>
+          <t>40,31; 57,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,26; 60,31</t>
+          <t>42,79; 58,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,33; 50,7</t>
+          <t>37,22; 51,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,72; 96,79</t>
+          <t>90,59; 97,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,14; 57,58</t>
+          <t>41,38; 57,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,34; 56,63</t>
+          <t>41,03; 57,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,02; 52,81</t>
+          <t>38,76; 52,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,02; 97,51</t>
+          <t>91,78; 97,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,7; 54,78</t>
+          <t>42,91; 54,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,62; 56,37</t>
+          <t>44,78; 56,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,97; 50,04</t>
+          <t>39,74; 49,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,54; 96,62</t>
+          <t>92,1; 96,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 49,89</t>
+          <t>36,78; 49,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,44; 57,67</t>
+          <t>41,6; 56,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,34; 61,8</t>
+          <t>45,55; 61,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,32; 97,76</t>
+          <t>93,48; 97,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,88; 55,92</t>
+          <t>43,07; 56,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,56; 65,16</t>
+          <t>50,85; 64,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,01; 56,79</t>
+          <t>40,48; 55,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,18; 97,02</t>
+          <t>91,82; 97,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,43; 50,54</t>
+          <t>41,66; 50,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,85; 59,23</t>
+          <t>48,69; 58,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,25; 56,82</t>
+          <t>46,2; 57,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,5; 96,93</t>
+          <t>93,6; 96,91</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,33; 43,1</t>
+          <t>35,99; 43,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 50,27</t>
+          <t>42,91; 50,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,05; 46,81</t>
+          <t>39,25; 45,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,65; 96,55</t>
+          <t>93,73; 96,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 46,14</t>
+          <t>39,5; 46,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,4; 51,25</t>
+          <t>44,59; 51,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,56</t>
+          <t>37,51; 44,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,96; 96,1</t>
+          <t>93,06; 96,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,91; 43,8</t>
+          <t>38,72; 43,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,72; 50,14</t>
+          <t>44,74; 49,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,18; 44,09</t>
+          <t>39,26; 44,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,79; 95,86</t>
+          <t>93,84; 95,98</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20460; 34106</t>
+          <t>20730; 33792</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33287; 48661</t>
+          <t>32367; 48609</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25034; 39343</t>
+          <t>24591; 39869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48560; 55320</t>
+          <t>48458; 54979</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25370; 39072</t>
+          <t>25560; 39757</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38926; 56765</t>
+          <t>38210; 56341</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28787; 43608</t>
+          <t>29320; 44782</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57596; 61056</t>
+          <t>57504; 61057</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50196; 69090</t>
+          <t>49455; 69534</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75867; 100224</t>
+          <t>76282; 100423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58103; 79580</t>
+          <t>58384; 79309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>108535; 115927</t>
+          <t>108649; 115609</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55716; 77526</t>
+          <t>56522; 76865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62712; 83215</t>
+          <t>64008; 83874</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51564; 70441</t>
+          <t>51112; 70212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148121; 155965</t>
+          <t>146844; 155585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60248; 80388</t>
+          <t>59516; 81170</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73687; 97323</t>
+          <t>73039; 96818</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63239; 85703</t>
+          <t>63536; 86339</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>163054; 174825</t>
+          <t>163162; 175105</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120397; 151311</t>
+          <t>120873; 151464</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143229; 175983</t>
+          <t>143308; 174878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120819; 150358</t>
+          <t>121090; 150252</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>313904; 328347</t>
+          <t>313909; 328781</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34155; 49076</t>
+          <t>34863; 49778</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42390; 59095</t>
+          <t>41921; 57599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53875; 73174</t>
+          <t>53710; 73690</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157745; 168305</t>
+          <t>157527; 168822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42486; 59457</t>
+          <t>42725; 59483</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42092; 57660</t>
+          <t>41774; 58777</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50254; 69798</t>
+          <t>51228; 69674</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>193402; 207189</t>
+          <t>195022; 207355</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81014; 103937</t>
+          <t>81423; 104281</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89148; 112632</t>
+          <t>89459; 112211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110502; 138360</t>
+          <t>109868; 138086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>357546; 373301</t>
+          <t>355847; 372428</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54927; 75373</t>
+          <t>55564; 74746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49025; 66616</t>
+          <t>48055; 65830</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56587; 75464</t>
+          <t>55622; 75103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257058; 269280</t>
+          <t>257500; 269107</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63510; 82819</t>
+          <t>63791; 83681</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66590; 85822</t>
+          <t>66967; 84861</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53317; 73825</t>
+          <t>52626; 72467</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>281585; 296381</t>
+          <t>280502; 296646</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>123946; 151196</t>
+          <t>124646; 151721</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120768; 146438</t>
+          <t>120368; 145181</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116601; 143243</t>
+          <t>116470; 143823</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>543189; 563111</t>
+          <t>543732; 562972</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182877; 216941</t>
+          <t>181145; 217000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>205564; 239769</t>
+          <t>204644; 239956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>205187; 245939</t>
+          <t>206228; 241106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>623857; 643158</t>
+          <t>624388; 642736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>208567; 243856</t>
+          <t>208778; 245146</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>239227; 276099</t>
+          <t>240217; 278303</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>216460; 254440</t>
+          <t>214222; 253416</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>708305; 732249</t>
+          <t>709120; 732502</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>401501; 451997</t>
+          <t>399580; 453282</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>454290; 509320</t>
+          <t>454476; 506927</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>429534; 483422</t>
+          <t>430455; 483498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1339500; 1368932</t>
+          <t>1340125; 1370764</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42,42%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>34,77%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39,22%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31,3%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,43%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,39; 43,01</t>
+          <t>28,15; 45,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,09; 46,69</t>
+          <t>35,15; 50,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,94; 38,82</t>
+          <t>30,48; 45,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,26; 95,6</t>
+          <t>94,45; 99,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,89; 44,94</t>
+          <t>26,44; 43,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,1; 50,29</t>
+          <t>31,0; 46,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,84; 45,57</t>
+          <t>24,28; 38,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,59; 99,37</t>
+          <t>85,38; 96,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,61; 41,63</t>
+          <t>29,48; 41,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,29; 46,46</t>
+          <t>35,08; 46,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,05; 39,46</t>
+          <t>29,11; 39,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,34; 97,19</t>
+          <t>91,66; 97,34</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>44,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>35,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>46,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>38,85%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>44,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,19; 41,05</t>
+          <t>31,75; 43,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,17; 52,64</t>
+          <t>38,48; 49,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,71; 44,93</t>
+          <t>30,52; 40,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,18; 97,67</t>
+          <t>90,76; 96,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,53; 43,01</t>
+          <t>30,22; 41,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 50,11</t>
+          <t>40,23; 53,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,17; 41,0</t>
+          <t>32,53; 45,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,38; 95,92</t>
+          <t>91,69; 97,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,15; 40,29</t>
+          <t>32,63; 40,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40,65; 49,6</t>
+          <t>41,21; 49,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,01; 40,96</t>
+          <t>33,03; 41,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,83; 96,18</t>
+          <t>92,44; 96,31</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,55%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>48,2%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>51,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>44,12%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,31; 57,56</t>
+          <t>41,49; 56,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,79; 58,79</t>
+          <t>40,74; 57,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,22; 51,06</t>
+          <t>38,5; 52,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,59; 97,09</t>
+          <t>90,89; 97,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,38; 57,6</t>
+          <t>39,41; 57,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,03; 57,73</t>
+          <t>42,72; 59,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,76; 52,71</t>
+          <t>37,41; 50,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,78; 97,58</t>
+          <t>90,58; 96,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,91; 54,96</t>
+          <t>43,44; 55,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,78; 56,16</t>
+          <t>44,97; 56,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,74; 49,94</t>
+          <t>39,91; 49,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,1; 96,39</t>
+          <t>91,93; 96,66</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57,75%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>42,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>49,6%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>54,17%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,78; 49,48</t>
+          <t>42,19; 55,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,6; 56,99</t>
+          <t>51,11; 64,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 61,51</t>
+          <t>41,35; 56,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,48; 97,69</t>
+          <t>91,46; 96,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,07; 56,51</t>
+          <t>36,58; 49,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,85; 64,43</t>
+          <t>42,02; 57,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,48; 55,74</t>
+          <t>46,63; 62,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,82; 97,11</t>
+          <t>92,61; 97,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,66; 50,71</t>
+          <t>41,09; 50,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,69; 58,73</t>
+          <t>48,48; 58,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,2; 57,05</t>
+          <t>45,44; 56,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,6; 96,91</t>
+          <t>93,13; 96,52</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 43,11</t>
+          <t>39,43; 46,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,31</t>
+          <t>44,3; 51,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,25; 45,89</t>
+          <t>37,88; 44,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,73; 96,48</t>
+          <t>93,03; 96,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,5; 46,38</t>
+          <t>36,09; 43,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,59; 51,65</t>
+          <t>43,08; 50,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,51; 44,38</t>
+          <t>38,94; 45,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,06; 96,13</t>
+          <t>93,2; 96,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,72; 43,93</t>
+          <t>38,83; 43,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,74; 49,91</t>
+          <t>44,8; 49,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,26; 44,1</t>
+          <t>39,31; 44,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,84; 95,98</t>
+          <t>93,67; 95,82</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32410</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47533</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36779</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49522</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>27312</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>40839</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>32149</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52736</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32410</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47533</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36779</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60123</t>
+          <t>48115</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>112858</t>
+          <t>97637</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20730; 33792</t>
+          <t>24900; 39906</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32367; 48609</t>
+          <t>39386; 56631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24591; 39869</t>
+          <t>29948; 44815</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48458; 54979</t>
+          <t>47731; 50244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25560; 39757</t>
+          <t>20769; 34051</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38210; 56341</t>
+          <t>32282; 48830</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29320; 44782</t>
+          <t>24933; 39674</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57504; 61057</t>
+          <t>44475; 50093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49455; 69534</t>
+          <t>49246; 69459</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76282; 100423</t>
+          <t>75841; 99695</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58384; 79309</t>
+          <t>58500; 79450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>108649; 115609</t>
+          <t>94064; 99895</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>246</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70104</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85128</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74341</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>147910</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>66552</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>74003</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>60715</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>152658</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70104</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85128</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74341</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>170180</t>
+          <t>138924</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>322838</t>
+          <t>286833</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56522; 76865</t>
+          <t>59925; 81310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64008; 83874</t>
+          <t>74344; 96553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51112; 70212</t>
+          <t>64275; 85640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146844; 155585</t>
+          <t>142971; 151860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59516; 81170</t>
+          <t>56590; 78108</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73039; 96818</t>
+          <t>64104; 84554</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63536; 86339</t>
+          <t>50837; 70915</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>163162; 175105</t>
+          <t>133426; 142040</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120873; 151464</t>
+          <t>122674; 152483</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143308; 174878</t>
+          <t>145310; 174925</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>121090; 150252</t>
+          <t>121165; 150844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>313909; 328781</t>
+          <t>280118; 291871</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>221</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50803</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50356</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60206</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>189826</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>41679</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>50258</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>63671</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>163938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50803</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50356</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60206</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>201945</t>
+          <t>165411</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>365883</t>
+          <t>355237</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34863; 49778</t>
+          <t>42845; 58573</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41921; 57599</t>
+          <t>41480; 58126</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53710; 73690</t>
+          <t>50884; 69412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157527; 168822</t>
+          <t>181900; 194654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42725; 59483</t>
+          <t>34080; 49398</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41774; 58777</t>
+          <t>41859; 57993</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51228; 69674</t>
+          <t>53992; 73493</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>195022; 207355</t>
+          <t>158979; 170038</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81423; 104281</t>
+          <t>82429; 104612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89459; 112211</t>
+          <t>89847; 111978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109868; 138086</t>
+          <t>110353; 136055</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>355847; 372428</t>
+          <t>345332; 363097</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>326</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>72916</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>76055</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63292</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>276941</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>64602</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>57295</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>66139</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>264336</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>72916</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76055</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63292</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>289921</t>
+          <t>245029</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>554255</t>
+          <t>521970</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55564; 74746</t>
+          <t>62482; 81854</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48055; 65830</t>
+          <t>67306; 85268</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55622; 75103</t>
+          <t>53751; 73007</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257500; 269107</t>
+          <t>267644; 283465</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63791; 83681</t>
+          <t>55263; 75364</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66967; 84861</t>
+          <t>48537; 65868</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52626; 72467</t>
+          <t>56942; 75934</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>280502; 296646</t>
+          <t>237602; 249671</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124646; 151721</t>
+          <t>122940; 150593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120368; 145181</t>
+          <t>119844; 144855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116470; 143823</t>
+          <t>114569; 141637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>543732; 562972</t>
+          <t>511494; 530086</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>893</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>633667</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>597478</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1355836</t>
+          <t>1261676</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>181145; 217000</t>
+          <t>208384; 245623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204644; 239956</t>
+          <t>238688; 276489</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206228; 241106</t>
+          <t>216293; 255101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>624388; 642736</t>
+          <t>651951; 673502</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>208778; 245146</t>
+          <t>181684; 218077</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>240217; 278303</t>
+          <t>205485; 239569</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>214222; 253416</t>
+          <t>204609; 239933</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>709120; 732502</t>
+          <t>586887; 605754</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>399580; 453282</t>
+          <t>400649; 450187</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>454476; 506927</t>
+          <t>455074; 505661</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>430455; 483498</t>
+          <t>431014; 485340</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1340125; 1370764</t>
+          <t>1246306; 1274903</t>
         </is>
       </c>
     </row>
